--- a/config/_TableConfig/!enums__.xlsx
+++ b/config/_TableConfig/!enums__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31050" windowHeight="11380"/>
+    <workbookView windowWidth="18770" windowHeight="14390"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
